--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875612</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875606</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875609</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875587</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875594</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875593</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875595</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875588</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875591</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875578</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875580</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875583</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2029,6 +2094,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875589</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2131,6 +2201,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875610</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2242,6 +2317,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009897</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2353,6 +2433,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009887</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2464,6 +2549,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009888</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2575,6 +2665,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010377</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2681,6 +2776,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875581</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2787,6 +2887,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875585</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875592</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875596</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875607</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875611</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3313,6 +3438,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875614</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3419,6 +3549,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875615</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3525,6 +3660,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875616</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3632,6 +3772,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875579</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3739,6 +3884,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875582</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3846,6 +3996,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875590</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3953,8 +4108,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96601</v>
+        <v>96772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96601</v>
+        <v>96772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96773</v>
+        <v>96774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96773</v>
+        <v>96774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96774</v>
+        <v>96780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96774</v>
+        <v>96780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96780</v>
+        <v>96781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96780</v>
+        <v>96781</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96781</v>
+        <v>96792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96781</v>
+        <v>96792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96792</v>
+        <v>96805</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96792</v>
+        <v>96805</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96805</v>
+        <v>96806</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96805</v>
+        <v>96806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96806</v>
+        <v>96819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96806</v>
+        <v>96819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96819</v>
+        <v>96820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96819</v>
+        <v>96820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
